--- a/data/trans_orig/POLIPATOLOGIA_Lim_5-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/POLIPATOLOGIA_Lim_5-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cinco o más enfermedades crónicas de las que al menos una es limitante en 2012</t>
+          <t>Población con cinco o más enfermedades crónicas de las que al menos una es limitante en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>72621</t>
+          <t>72224</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>110635</t>
+          <t>110982</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>227015</t>
+          <t>228122</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>287003</t>
+          <t>287255</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>308357</t>
+          <t>311038</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>381561</t>
+          <t>380209</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,44%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>864008</t>
+          <t>863661</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>902022</t>
+          <t>902419</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1050794</t>
+          <t>1050542</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1110782</t>
+          <t>1109675</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1930879</t>
+          <t>1932231</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2004083</t>
+          <t>2001402</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>86,55%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17353</t>
+          <t>17461</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37009</t>
+          <t>38393</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>47878</t>
+          <t>48024</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>82050</t>
+          <t>83253</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>70350</t>
+          <t>70829</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>112351</t>
+          <t>109940</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1926948</t>
+          <t>1925564</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1946604</t>
+          <t>1946496</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1675753</t>
+          <t>1674550</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1709925</t>
+          <t>1709779</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3609409</t>
+          <t>3611820</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3651410</t>
+          <t>3650931</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,1%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1953</t>
+          <t>1951</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>15295</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5924</t>
+          <t>5906</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21473</t>
+          <t>20955</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10039</t>
+          <t>10131</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30750</t>
+          <t>29942</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>466760</t>
+          <t>465886</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>479228</t>
+          <t>479230</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>437158</t>
+          <t>437676</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>452707</t>
+          <t>452725</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>909063</t>
+          <t>909871</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>929774</t>
+          <t>929682</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,92%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>102545</t>
+          <t>101568</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>148347</t>
+          <t>146968</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>295958</t>
+          <t>295471</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>368998</t>
+          <t>366084</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>409661</t>
+          <t>410457</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>496641</t>
+          <t>497413</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,13%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3271435</t>
+          <t>3272814</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3317237</t>
+          <t>3318214</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3185232</t>
+          <t>3188146</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3258272</t>
+          <t>3258759</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6477371</t>
+          <t>6476599</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6564351</t>
+          <t>6563555</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,11%</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cinco o más enfermedades crónicas de las que al menos una es limitante en 2016</t>
+          <t>Población con cinco o más enfermedades crónicas de las que al menos una es limitante en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2335,12 +2335,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>46210</t>
+          <t>47134</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>74690</t>
+          <t>74145</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>170411</t>
+          <t>170394</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>224314</t>
+          <t>222085</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>225175</t>
+          <t>224110</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>286718</t>
+          <t>287131</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,42%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>679657</t>
+          <t>680202</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>708137</t>
+          <t>707213</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>770346</t>
+          <t>772575</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>824249</t>
+          <t>824266</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1462289</t>
+          <t>1461876</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1523832</t>
+          <t>1524897</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>87,19%</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25625</t>
+          <t>24788</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>50195</t>
+          <t>49880</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>85078</t>
+          <t>86178</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>127895</t>
+          <t>130783</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>117911</t>
+          <t>115000</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>165494</t>
+          <t>164720</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2026190</t>
+          <t>2026505</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2050760</t>
+          <t>2051597</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1860405</t>
+          <t>1857517</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1903222</t>
+          <t>1902122</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3899191</t>
+          <t>3899965</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3946774</t>
+          <t>3949685</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,17%</t>
         </is>
       </c>
     </row>
@@ -3021,12 +3021,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5585</t>
+          <t>5113</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20718</t>
+          <t>19727</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9064</t>
+          <t>9375</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26694</t>
+          <t>27878</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17253</t>
+          <t>17760</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>40822</t>
+          <t>41190</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>526168</t>
+          <t>527159</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>541301</t>
+          <t>541773</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>522446</t>
+          <t>521262</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>540076</t>
+          <t>539765</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1055205</t>
+          <t>1054837</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1078774</t>
+          <t>1078267</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,38%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>86909</t>
+          <t>88014</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>128270</t>
+          <t>126840</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>282941</t>
+          <t>281104</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>353645</t>
+          <t>351057</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>377100</t>
+          <t>380597</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>464667</t>
+          <t>465165</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,73%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3249348</t>
+          <t>3250778</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3290709</t>
+          <t>3289604</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3178455</t>
+          <t>3181043</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3249159</t>
+          <t>3250996</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6445051</t>
+          <t>6444553</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6532618</t>
+          <t>6529121</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,49%</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cinco o más enfermedades crónicas de las que al menos una es limitante en 2023</t>
+          <t>Población con cinco o más enfermedades crónicas de las que al menos una es limitante en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3938,12 +3938,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>89421</t>
+          <t>90327</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>121213</t>
+          <t>121998</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>245797</t>
+          <t>244563</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>287559</t>
+          <t>286106</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>344582</t>
+          <t>345652</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>400275</t>
+          <t>398842</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4023,12 +4023,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,39%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>393725</t>
+          <t>392940</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>425517</t>
+          <t>424611</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>76,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>467949</t>
+          <t>469402</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>509711</t>
+          <t>510945</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,94%</t>
+          <t>62,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,47%</t>
+          <t>67,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>870171</t>
+          <t>871604</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>925864</t>
+          <t>924794</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,88%</t>
+          <t>72,79%</t>
         </is>
       </c>
     </row>
@@ -4281,12 +4281,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>75684</t>
+          <t>74168</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>131136</t>
+          <t>132127</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4296,12 +4296,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4316,12 +4316,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>144983</t>
+          <t>145539</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>234352</t>
+          <t>233386</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4331,12 +4331,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>245458</t>
+          <t>251977</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>354337</t>
+          <t>350575</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,74%</t>
         </is>
       </c>
     </row>
@@ -4394,12 +4394,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2159191</t>
+          <t>2158200</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2214643</t>
+          <t>2216159</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2003471</t>
+          <t>2004437</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2092840</t>
+          <t>2092284</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4173813</t>
+          <t>4177575</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4282692</t>
+          <t>4276173</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,44%</t>
         </is>
       </c>
     </row>
@@ -4624,12 +4624,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9479</t>
+          <t>9845</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23700</t>
+          <t>25106</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4659,12 +4659,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>40897</t>
+          <t>40783</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>64330</t>
+          <t>63761</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4694,12 +4694,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>53963</t>
+          <t>53720</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>80676</t>
+          <t>80415</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4709,12 +4709,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -4737,12 +4737,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>622923</t>
+          <t>621517</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>637144</t>
+          <t>636778</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>596133</t>
+          <t>596702</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>619566</t>
+          <t>619680</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1226410</t>
+          <t>1226671</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1253123</t>
+          <t>1253366</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4822,12 +4822,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,89%</t>
         </is>
       </c>
     </row>
@@ -4967,12 +4967,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>175782</t>
+          <t>179574</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>263310</t>
+          <t>259704</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>415294</t>
+          <t>420082</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>565516</t>
+          <t>565321</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>654889</t>
+          <t>640429</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>811403</t>
+          <t>811943</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5052,12 +5052,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,43%</t>
         </is>
       </c>
     </row>
@@ -5080,12 +5080,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3188579</t>
+          <t>3192185</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3276107</t>
+          <t>3272315</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5115,12 +5115,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3088278</t>
+          <t>3088473</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3238500</t>
+          <t>3233712</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6294280</t>
+          <t>6293740</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6450794</t>
+          <t>6465254</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5165,12 +5165,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,99%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/POLIPATOLOGIA_Lim_5-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/POLIPATOLOGIA_Lim_5-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>72224</t>
+          <t>73012</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>110982</t>
+          <t>109925</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>228122</t>
+          <t>227095</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>287255</t>
+          <t>285265</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>311038</t>
+          <t>310855</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>380209</t>
+          <t>386832</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,73%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>863661</t>
+          <t>864718</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>902419</t>
+          <t>901631</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1050542</t>
+          <t>1052532</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1109675</t>
+          <t>1110702</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>78,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1932231</t>
+          <t>1925608</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2001402</t>
+          <t>2001585</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,56%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17461</t>
+          <t>16141</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38393</t>
+          <t>36618</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>48024</t>
+          <t>47689</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>83253</t>
+          <t>81940</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>70829</t>
+          <t>70815</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>109940</t>
+          <t>109516</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1925564</t>
+          <t>1927339</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1946496</t>
+          <t>1947816</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1674550</t>
+          <t>1675863</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1709779</t>
+          <t>1710114</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3611820</t>
+          <t>3612244</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3650931</t>
+          <t>3650945</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1951</t>
+          <t>1984</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15295</t>
+          <t>18009</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5906</t>
+          <t>6453</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20955</t>
+          <t>21950</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10131</t>
+          <t>9789</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29942</t>
+          <t>29437</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>465886</t>
+          <t>463172</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>479230</t>
+          <t>479197</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>437676</t>
+          <t>436681</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>452725</t>
+          <t>452178</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>909871</t>
+          <t>910376</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>929682</t>
+          <t>930024</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>101568</t>
+          <t>100733</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>146968</t>
+          <t>146548</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>295471</t>
+          <t>297589</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>366084</t>
+          <t>366391</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>410457</t>
+          <t>409917</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>497413</t>
+          <t>496284</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3272814</t>
+          <t>3273234</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3318214</t>
+          <t>3319049</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3188146</t>
+          <t>3187839</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3258759</t>
+          <t>3256641</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6476599</t>
+          <t>6477728</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6563555</t>
+          <t>6564095</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,12%</t>
         </is>
       </c>
     </row>
@@ -2335,12 +2335,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>47134</t>
+          <t>47711</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>74145</t>
+          <t>74647</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>170394</t>
+          <t>169581</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>222085</t>
+          <t>224000</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>224110</t>
+          <t>225134</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>287131</t>
+          <t>286785</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,4%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>680202</t>
+          <t>679700</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>707213</t>
+          <t>706636</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>772575</t>
+          <t>770660</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>824266</t>
+          <t>825079</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,67%</t>
+          <t>77,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1461876</t>
+          <t>1462222</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1524897</t>
+          <t>1523873</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>87,13%</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24788</t>
+          <t>24030</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49880</t>
+          <t>49378</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>86178</t>
+          <t>84783</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>130783</t>
+          <t>126054</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>115000</t>
+          <t>114651</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>164720</t>
+          <t>165941</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2026505</t>
+          <t>2027007</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2051597</t>
+          <t>2052355</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1857517</t>
+          <t>1862246</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1902122</t>
+          <t>1903517</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3899965</t>
+          <t>3898744</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3949685</t>
+          <t>3950034</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,18%</t>
         </is>
       </c>
     </row>
@@ -3021,12 +3021,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5113</t>
+          <t>5212</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19727</t>
+          <t>20459</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9375</t>
+          <t>9138</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27878</t>
+          <t>27959</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17760</t>
+          <t>16802</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>41190</t>
+          <t>39970</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>527159</t>
+          <t>526427</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>541773</t>
+          <t>541674</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>521262</t>
+          <t>521181</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>539765</t>
+          <t>540002</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1054837</t>
+          <t>1056057</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1078267</t>
+          <t>1079225</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,47%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>88014</t>
+          <t>89022</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>126840</t>
+          <t>127751</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>281104</t>
+          <t>283021</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>351057</t>
+          <t>354811</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>380597</t>
+          <t>384670</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>465165</t>
+          <t>465375</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3250778</t>
+          <t>3249867</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3289604</t>
+          <t>3288596</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3181043</t>
+          <t>3177289</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3250996</t>
+          <t>3249079</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6444553</t>
+          <t>6444343</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6529121</t>
+          <t>6525048</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,43%</t>
         </is>
       </c>
     </row>
@@ -3933,32 +3933,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>105379</t>
+          <t>112067</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>90327</t>
+          <t>97577</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>121998</t>
+          <t>132747</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3968,32 +3968,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>265780</t>
+          <t>283241</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>244563</t>
+          <t>263762</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>286106</t>
+          <t>304123</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4003,32 +4003,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>371159</t>
+          <t>395308</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>345652</t>
+          <t>367531</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>398842</t>
+          <t>424330</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>30,3%</t>
         </is>
       </c>
     </row>
@@ -4046,32 +4046,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>409559</t>
+          <t>466462</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>392940</t>
+          <t>445782</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>424611</t>
+          <t>480952</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>80,63%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>77,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4081,32 +4081,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>489728</t>
+          <t>538797</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>469402</t>
+          <t>517915</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>510945</t>
+          <t>558276</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>64,82%</t>
+          <t>65,54%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>63,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,63%</t>
+          <t>67,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4116,32 +4116,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>899287</t>
+          <t>1005259</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>871604</t>
+          <t>976237</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>924794</t>
+          <t>1033036</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>70,79%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,61%</t>
+          <t>69,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>73,76%</t>
         </is>
       </c>
     </row>
@@ -4159,17 +4159,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4194,17 +4194,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4229,17 +4229,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4276,32 +4276,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>108625</t>
+          <t>116543</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>74168</t>
+          <t>97480</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>132127</t>
+          <t>137252</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4311,32 +4311,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>199953</t>
+          <t>219879</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>145539</t>
+          <t>197763</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>233386</t>
+          <t>243963</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>308578</t>
+          <t>336423</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>251977</t>
+          <t>309717</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>350575</t>
+          <t>368015</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,36%</t>
         </is>
       </c>
     </row>
@@ -4389,32 +4389,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2181702</t>
+          <t>2114023</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2158200</t>
+          <t>2093314</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2216159</t>
+          <t>2133086</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4424,32 +4424,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2037870</t>
+          <t>1951513</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2004437</t>
+          <t>1927429</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2092284</t>
+          <t>1973629</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4459,32 +4459,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4219572</t>
+          <t>4065536</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4177575</t>
+          <t>4033944</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4276173</t>
+          <t>4092242</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>92,96%</t>
         </is>
       </c>
     </row>
@@ -4502,17 +4502,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4537,17 +4537,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4572,17 +4572,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4619,32 +4619,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>15907</t>
+          <t>17423</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9845</t>
+          <t>10676</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25106</t>
+          <t>27752</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4654,32 +4654,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>50518</t>
+          <t>57183</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>40783</t>
+          <t>45947</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>63761</t>
+          <t>70379</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4689,32 +4689,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>66425</t>
+          <t>74605</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>53720</t>
+          <t>61071</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>80415</t>
+          <t>89079</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,16%</t>
         </is>
       </c>
     </row>
@@ -4732,32 +4732,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>630716</t>
+          <t>694164</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>621517</t>
+          <t>683835</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>636778</t>
+          <t>700911</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4767,32 +4767,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>609945</t>
+          <t>677694</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>596702</t>
+          <t>664498</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>619680</t>
+          <t>688930</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4802,32 +4802,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1240661</t>
+          <t>1371859</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1226671</t>
+          <t>1357385</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1253366</t>
+          <t>1385393</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,78%</t>
         </is>
       </c>
     </row>
@@ -4845,17 +4845,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4880,17 +4880,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4915,17 +4915,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4962,32 +4962,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>229911</t>
+          <t>246033</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>179574</t>
+          <t>218383</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>259704</t>
+          <t>277044</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4997,32 +4997,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>516251</t>
+          <t>560303</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>420082</t>
+          <t>526935</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>565321</t>
+          <t>597066</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
+          <t>15,03%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
           <t>14,13%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>11,5%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5032,32 +5032,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>746162</t>
+          <t>806336</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>640429</t>
+          <t>761804</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>811943</t>
+          <t>855725</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,8%</t>
         </is>
       </c>
     </row>
@@ -5075,32 +5075,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3221978</t>
+          <t>3274650</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3192185</t>
+          <t>3243639</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3272315</t>
+          <t>3302300</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5110,34 +5110,34 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3137543</t>
+          <t>3168004</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3088473</t>
+          <t>3131241</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3233712</t>
+          <t>3201372</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
+          <t>84,97%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>83,99%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
           <t>85,87%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>84,53%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>88,5%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>7427</t>
@@ -5145,32 +5145,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6359521</t>
+          <t>6442654</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6293740</t>
+          <t>6393265</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6465254</t>
+          <t>6487186</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>89,49%</t>
         </is>
       </c>
     </row>
@@ -5188,17 +5188,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5223,17 +5223,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5258,17 +5258,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
